--- a/learning/phase2b_project1/08_fpa_model.xlsx
+++ b/learning/phase2b_project1/08_fpa_model.xlsx
@@ -8130,8 +8130,8 @@
     <row r="20" ht="50" customHeight="1" s="130">
       <c r="A20" s="129" t="inlineStr">
         <is>
-          <t>Paragraph 2 — OpEx &amp; EBITDA:
-EBITDA fell short by AED 91K (-10.1%) for the quarter, driven by two factors: a cumulative gross profit miss of AED 229K and an OpEx overspend of AED 70K (+3.4%). Marketing costs ran above plan in all three months, with March showing the largest deviation at AED 43K above budget. The combined effect compressed EBITDA margin by approximately 4.5 percentage points versus budget.</t>
+          <t>Paragraph 2 — OpEx &amp; Operating Profit:
+Operating Profit fell short by AED 141K (-10.1%) for the quarter, driven by two factors: a cumulative gross profit miss of AED 74K and an OpEx overspend of AED 70K (+3.4%). Marketing costs ran above plan in all three months, with March showing the largest deviation at AED 43K above budget. The combined effect compressed operating margin by 200 basis points (2.0pp) versus budget.</t>
         </is>
       </c>
     </row>
